--- a/trading_signals/risk_management/risk_workbook_20260616_000000.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260616_000000.xlsx
@@ -109,12 +109,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
+        <fgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
+        <fgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -187,19 +187,19 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -351,12 +351,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'NAV Trend'!$A$4:$A$159</f>
+              <f>'NAV Trend'!$A$4:$A$158</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'NAV Trend'!$B$4:$B$159</f>
+              <f>'NAV Trend'!$B$4:$B$158</f>
             </numRef>
           </val>
         </ser>
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-16  ·  Generated 2026-06-24T21:36:44  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-15  ·  Generated 2026-06-25T01:49:59  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1121042.13</v>
+        <v>1149704.73</v>
       </c>
     </row>
     <row r="5">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1.046</v>
+        <v>1.264</v>
       </c>
     </row>
     <row r="6">
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.431</v>
+        <v>0.533</v>
       </c>
     </row>
     <row r="7">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1.321</v>
+        <v>1.355</v>
       </c>
     </row>
     <row r="8">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>29530.01</v>
+        <v>31897.36</v>
       </c>
     </row>
     <row r="9">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="10">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>25.42</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="11">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.42</v>
+        <v>1.606</v>
       </c>
     </row>
     <row r="12">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.8699</v>
+        <v>0.8974</v>
       </c>
     </row>
     <row r="13">
@@ -840,7 +840,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>4.96 / 2.48</t>
+          <t>5.74 / 2.87</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1.046</v>
+        <v>1.264</v>
       </c>
     </row>
     <row r="16">
@@ -862,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>KLAC (24.13% NAV)</t>
+          <t>KLAC (25.43% NAV)</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>37.79</v>
+        <v>32.81</v>
       </c>
     </row>
     <row r="18">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -904,7 +904,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>net_market_beta:combined red</t>
+          <t>net_leverage_abs:mtfs red</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>29530.01</v>
+        <v>31897.36</v>
       </c>
     </row>
     <row r="4">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>41754.9</v>
+        <v>45102.29</v>
       </c>
     </row>
     <row r="5">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>284969.25</v>
+        <v>307814.55</v>
       </c>
     </row>
     <row r="6">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>25.42</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="7">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>16119.33</v>
+        <v>15850.49</v>
       </c>
     </row>
     <row r="8">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>30116.89</v>
+        <v>26690.34</v>
       </c>
     </row>
     <row r="10">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>7460.3</v>
+        <v>7016.45</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>25.26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>7456.14</v>
+        <v>6668.92</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>25.25</v>
+        <v>20.91</v>
       </c>
     </row>
     <row r="14">
@@ -1054,62 +1054,75 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>5492.5</v>
+        <v>4902.74</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>18.6</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>3729.93</v>
+        <v>4406.14</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>12.63</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>ODFL/PLTR</t>
+          <t>LRCX/NRG</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2051.05</v>
+        <v>3506.35</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>6.95</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>1687.49</v>
+        <v>1916.97</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>5.71</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>ODFL/PLTR</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1652.61</v>
+        <v>1821.41</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>5.6</v>
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>NUE/MKTX</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>1658.38</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>5.2</v>
       </c>
     </row>
   </sheetData>
@@ -1126,7 +1139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1180,28 +1193,28 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>670</v>
+        <v>6843</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5871551</v>
+        <v>3141136</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
@@ -1209,11 +1222,11 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
-        <v>23</v>
+      <c r="C7" s="12" t="n">
+        <v>670</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>1100599</v>
+        <v>5216478</v>
       </c>
       <c r="E7" s="16" t="n">
         <v>0</v>
@@ -1222,19 +1235,19 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>329</v>
+          <t>KLAC/REGN</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>23</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1470419</v>
+        <v>1094195</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1243,7 +1256,7 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
@@ -1252,10 +1265,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>422</v>
+        <v>329</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>750048</v>
+        <v>1464440</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>0</v>
@@ -1264,19 +1277,19 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1131108</v>
+        <v>735990</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -1285,7 +1298,7 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
@@ -1294,10 +1307,10 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>999944</v>
+        <v>1107061</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>0</v>
@@ -1306,19 +1319,19 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>KLAC/TRMB</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>470</v>
+        <v>358</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5871551</v>
+        <v>1013207</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -1327,19 +1340,19 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>KLAC/TRMB</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>972</v>
+        <v>628</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>2889043</v>
+        <v>1107061</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>0</v>
@@ -1348,19 +1361,19 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>309</v>
+        <v>470</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8711508</v>
+        <v>5216478</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -1374,14 +1387,14 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>1466</v>
+        <v>972</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>2889043</v>
+        <v>2848836</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>0</v>
@@ -1390,19 +1403,19 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>AMAT/TRMB</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>10234157</v>
+        <v>8579449</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1411,19 +1424,19 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>AMAT/TRMB</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>395</v>
+        <v>1466</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>2478671</v>
+        <v>2848836</v>
       </c>
       <c r="E17" s="16" t="n">
         <v>0</v>
@@ -1432,19 +1445,19 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>ODFL/PLTR</t>
+          <t>LRCX/NRG</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>394</v>
+        <v>269</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1912590</v>
+        <v>10063064</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -1453,21 +1466,42 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
+          <t>LRCX/NRG</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>395</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>2510698</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>ODFL</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
           <t>ODFL/PLTR</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
-        <v>372</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>38774742</v>
-      </c>
-      <c r="E19" s="16" t="n">
+      <c r="C20" s="4" t="n">
+        <v>394</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>1871882</v>
+      </c>
+      <c r="E20" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1524,10 +1558,10 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>-74044.83</v>
-      </c>
-      <c r="C4" s="22" t="n">
-        <v>-6.61</v>
+        <v>-77892.5</v>
+      </c>
+      <c r="C4" s="21" t="n">
+        <v>-6.78</v>
       </c>
     </row>
     <row r="5">
@@ -1536,11 +1570,11 @@
           <t>SPY -10%</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
-        <v>-148089.67</v>
-      </c>
-      <c r="C5" s="20" t="n">
-        <v>-13.21</v>
+      <c r="B5" s="22" t="n">
+        <v>-155784.99</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>-13.55</v>
       </c>
     </row>
     <row r="6">
@@ -1550,10 +1584,10 @@
         </is>
       </c>
       <c r="B6" s="18" t="n">
-        <v>-74044.83</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>-6.61</v>
+        <v>-77892.5</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>-6.78</v>
       </c>
     </row>
     <row r="7">
@@ -1562,11 +1596,11 @@
           <t>Top sector -10%</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
-        <v>-44318.3</v>
-      </c>
-      <c r="C7" s="20" t="n">
-        <v>-3.95</v>
+      <c r="B7" s="22" t="n">
+        <v>-47677.02</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>-4.15</v>
       </c>
     </row>
   </sheetData>
@@ -1697,7 +1731,7 @@
         </is>
       </c>
       <c r="C6" s="30" t="n">
-        <v>2.13</v>
+        <v>2.49</v>
       </c>
       <c r="D6" s="30" t="n">
         <v>3</v>
@@ -1723,7 +1757,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>0.88</v>
+        <v>1.05</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1733,7 +1767,7 @@
       </c>
       <c r="F7" s="32" t="inlineStr">
         <is>
-          <t>amber</t>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1783,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>24.13</v>
+        <v>25.43</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>15</v>
@@ -1759,135 +1793,135 @@
       </c>
       <c r="F8" s="32" t="inlineStr">
         <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>single_name_gross</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>STLD</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
           <t>amber</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>single_name_gross</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>AMAT</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n">
-        <v>15.66</v>
-      </c>
-      <c r="D9" s="32" t="n">
+      <c r="C10" s="34" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="D10" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="E10" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="F9" s="32" t="inlineStr">
+      <c r="F10" s="34" t="inlineStr">
         <is>
           <t>amber</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>single_name_gross</t>
-        </is>
-      </c>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>TRMB</t>
-        </is>
-      </c>
-      <c r="C10" s="30" t="n">
-        <v>11.04</v>
-      </c>
-      <c r="D10" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" s="30" t="n">
-        <v>25</v>
-      </c>
-      <c r="F10" s="30" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>sector_net</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>max_pair</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>35</v>
+      </c>
+      <c r="F12" s="30" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>sector_net</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="n">
-        <v>37.79</v>
-      </c>
-      <c r="D11" s="32" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" s="32" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>max_pair</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>net_market_beta</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>combined</t>
         </is>
       </c>
-      <c r="C12" s="32" t="n">
-        <v>21.32</v>
-      </c>
-      <c r="D12" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="E12" s="32" t="n">
-        <v>35</v>
-      </c>
-      <c r="F12" s="32" t="inlineStr">
-        <is>
-          <t>amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>net_market_beta</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>combined</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="D13" s="34" t="n">
+      <c r="C13" s="32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="D13" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="E13" s="34" t="n">
+      <c r="E13" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="F13" s="34" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>red</t>
         </is>
@@ -1905,7 +1939,7 @@
         </is>
       </c>
       <c r="C14" s="30" t="n">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="D14" s="30" t="n">
         <v>3</v>
@@ -1944,26 +1978,26 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>open_pairs</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>mtfs</t>
         </is>
       </c>
-      <c r="C16" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" s="30" t="n">
+      <c r="C16" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="D16" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
@@ -1981,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2080,10 +2114,10 @@
         <v>670</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>237.33</v>
+        <v>256.42</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>159011.1</v>
+        <v>171801.4</v>
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
@@ -2124,10 +2158,10 @@
         <v>-23</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>614.73</v>
+        <v>614.98</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>-14138.79</v>
+        <v>-14144.54</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
@@ -2168,10 +2202,10 @@
         <v>329</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>259.08</v>
+        <v>259.32</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>85237.32000000001</v>
+        <v>85316.28</v>
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
@@ -2212,10 +2246,10 @@
         <v>-422</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>124.81</v>
+        <v>121</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-52669.82</v>
+        <v>-51062</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
@@ -2256,10 +2290,10 @@
         <v>386</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>274.29</v>
+        <v>272.19</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>105875.94</v>
+        <v>105065.34</v>
       </c>
       <c r="H8" s="16" t="inlineStr">
         <is>
@@ -2300,10 +2334,10 @@
         <v>-358</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>146.9</v>
+        <v>145.97</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>-52590.2</v>
+        <v>-52257.26</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -2327,12 +2361,12 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>KLAC/TRMB</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
@@ -2341,17 +2375,17 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>470</v>
+        <v>628</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>237.33</v>
+        <v>272.19</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>111545.1</v>
+        <v>170935.32</v>
       </c>
       <c r="H10" s="16" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>materials</t>
         </is>
       </c>
       <c r="I10" s="16" t="n">
@@ -2359,7 +2393,7 @@
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>monthly_aligned_windows</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2371,12 +2405,12 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>KLAC/TRMB</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2385,17 +2419,17 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-972</v>
+        <v>-6843</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>50.78</v>
+        <v>11.51</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>-49358.16</v>
+        <v>-78762.92999999999</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>industrial</t>
+          <t>food</t>
         </is>
       </c>
       <c r="I11" s="7" t="n">
@@ -2403,7 +2437,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>monthly_aligned_windows</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2415,12 +2449,12 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
@@ -2429,13 +2463,13 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>309</v>
+        <v>470</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>568.23</v>
+        <v>256.42</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>175583.07</v>
+        <v>120517.4</v>
       </c>
       <c r="H12" s="16" t="inlineStr">
         <is>
@@ -2447,7 +2481,7 @@
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2493,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -2473,13 +2507,13 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-1466</v>
+        <v>-972</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>50.78</v>
+        <v>50.21</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>-74443.48</v>
+        <v>-48804.12</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -2491,7 +2525,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2537,12 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>AMAT/TRMB</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -2517,13 +2551,13 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>369.08</v>
+        <v>585.78</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>99282.52</v>
+        <v>181006.02</v>
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
@@ -2535,7 +2569,7 @@
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>let_profits_run</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2581,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>AMAT/TRMB</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2561,17 +2595,17 @@
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-395</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>132.1</v>
+        <v>-1466</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>50.21</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>-52179.5</v>
+        <v>-73607.86</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>utilities</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="I15" s="7" t="n">
@@ -2579,7 +2613,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>let_profits_run</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2591,12 +2625,12 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>ODFL/PLTR</t>
+          <t>LRCX/NRG</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -2605,17 +2639,17 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>394</v>
+        <v>269</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>231.62</v>
+        <v>388.92</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>91258.28</v>
+        <v>104619.48</v>
       </c>
       <c r="H16" s="16" t="inlineStr">
         <is>
-          <t>industrial</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I16" s="16" t="n">
@@ -2623,7 +2657,7 @@
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>weekly_aligned_windows</t>
+          <t>let_profits_run</t>
         </is>
       </c>
     </row>
@@ -2635,37 +2669,125 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
+          <t>LRCX/NRG</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>-395</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>-51508</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>utilities</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>let_profits_run</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>MTFS</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
           <t>ODFL/PLTR</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>ODFL</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>394</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>237.42</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>93543.48</v>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>weekly_aligned_windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>MTFS</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>ODFL/PLTR</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E19" s="24" t="n">
         <v>-372</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>133.25</v>
-      </c>
-      <c r="G17" s="18" t="n">
-        <v>-49569</v>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="F19" s="4" t="n">
+        <v>134.71</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>-50112.12</v>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="I19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
@@ -2685,7 +2807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2753,10 +2875,10 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>24705.44</v>
+        <v>37489.99</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>173149.89</v>
+        <v>185945.94</v>
       </c>
       <c r="E4" s="16" t="n">
         <v>0</v>
@@ -2784,10 +2906,10 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5194.38</v>
+        <v>6881.16</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>137907.14</v>
+        <v>136378.28</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
@@ -2815,10 +2937,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>1544</v>
+        <v>1066.34</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>158466.14</v>
+        <v>157322.6</v>
       </c>
       <c r="E6" s="16" t="n">
         <v>1</v>
@@ -2842,21 +2964,21 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>KLAC/TRMB</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>13103.95</v>
+        <v>328.09</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>160903.26</v>
+        <v>249698.25</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>monthly_aligned_windows</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2873,21 +2995,21 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>3673.83</v>
+        <v>22630.29</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>250026.55</v>
+        <v>169321.52</v>
       </c>
       <c r="E8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
@@ -2904,21 +3026,21 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="n">
-        <v>-1553.36</v>
+          <t>AMAT/TRMB</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>9932.4</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>151462.02</v>
+        <v>254613.88</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>let_profits_run</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -2935,24 +3057,55 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
+          <t>LRCX/NRG</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>4455.1</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>156127.48</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>let_profits_run</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>MTFS</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
           <t>ODFL/PLTR</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n">
-        <v>-7166.4</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>140827.28</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="C11" s="18" t="n">
+        <v>-5424.32</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>143655.6</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3012,12 +3165,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -3046,12 +3199,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3216,12 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3151,16 +3304,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>14.38</v>
+        <v>13.86</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="22" t="n">
-        <v>-13.93</v>
+      <c r="E6" s="21" t="n">
+        <v>-13.33</v>
       </c>
     </row>
     <row r="7">
@@ -3170,16 +3323,16 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>13.86</v>
+        <v>14.25</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>25.79</v>
+        <v>26.12</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="E7" s="21" t="n">
-        <v>11.93</v>
+      <c r="E7" s="19" t="n">
+        <v>11.88</v>
       </c>
     </row>
     <row r="8">
@@ -3189,16 +3342,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>24.59</v>
+        <v>23.81</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="22" t="n">
-        <v>-21.05</v>
+      <c r="E8" s="21" t="n">
+        <v>-20.24</v>
       </c>
     </row>
     <row r="9">
@@ -3208,16 +3361,16 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>47.17</v>
+        <v>48.09</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>70.22</v>
+        <v>69.77</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="E9" s="21" t="n">
-        <v>23.05</v>
+      <c r="E9" s="19" t="n">
+        <v>21.69</v>
       </c>
     </row>
     <row r="11">
@@ -3246,7 +3399,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>25.26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -3256,7 +3409,7 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>25.25</v>
+        <v>20.91</v>
       </c>
     </row>
     <row r="15">
@@ -3266,47 +3419,57 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>18.6</v>
+        <v>15.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>12.63</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>ODFL/PLTR</t>
+          <t>LRCX/NRG</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>6.95</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>5.71</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>ODFL/PLTR</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>5.6</v>
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>NUE/MKTX</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n">
+        <v>5.2</v>
       </c>
     </row>
   </sheetData>
@@ -3416,7 +3579,7 @@
           <t>COMBINED</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="20" t="n">
         <v>38.94</v>
       </c>
       <c r="C5" s="7" t="n">
@@ -3465,7 +3628,7 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="19" t="n">
         <v>47.74</v>
       </c>
       <c r="C6" s="16" t="n">
@@ -3514,7 +3677,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="20" t="n">
         <v>29.07</v>
       </c>
       <c r="C7" s="7" t="n">
@@ -3642,10 +3805,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.829</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>20.476</v>
+        <v>21.139</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -3654,10 +3817,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>2.405</v>
+        <v>2.372</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2.405</v>
+        <v>2.372</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -3670,10 +3833,10 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>-0.428</v>
+        <v>-0.417</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>2.619</v>
+        <v>2.603</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>0</v>
@@ -3682,13 +3845,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>1.576</v>
+        <v>1.583</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>1.642</v>
+        <v>1.647</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="6">
@@ -3698,10 +3861,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1.901</v>
+        <v>1.958</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>23.47</v>
+        <v>24.258</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -3710,10 +3873,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>5.167</v>
+        <v>5.091</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>5.167</v>
+        <v>5.091</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -3778,13 +3941,13 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.42</v>
+        <v>1.606</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.8699</v>
+        <v>0.8974</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>330</v>
+        <v>259</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>8.859999999999999</v>
@@ -3793,16 +3956,16 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>75</v>
+        <v>74.8</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>4.96</v>
+        <v>5.74</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>2.48</v>
+        <v>2.87</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.046</v>
+        <v>1.264</v>
       </c>
     </row>
     <row r="10">
@@ -3812,13 +3975,13 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>1.241</v>
+        <v>1.176</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>0.8293</v>
+        <v>0.8158</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>461</v>
+        <v>513</v>
       </c>
       <c r="E10" s="16" t="n">
         <v>9.35</v>
@@ -3827,13 +3990,13 @@
         <v>9.57</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>77.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>5.81</v>
+        <v>5.4</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="J10" s="16" t="n">
         <v>0</v>
@@ -3846,13 +4009,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1.152</v>
+        <v>1.345</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.8294</v>
+        <v>0.8678</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>461</v>
+        <v>333</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.56</v>
@@ -3861,16 +4024,16 @@
         <v>18.48</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>78.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>2.132</v>
+        <v>2.493</v>
       </c>
     </row>
   </sheetData>
@@ -3945,16 +4108,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>286349.82</v>
+        <v>108494.83</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>106099.17</v>
+        <v>130747.75</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>35966.64</v>
+        <v>169573.7</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>401161.07</v>
+        <v>492287.7</v>
       </c>
     </row>
     <row r="6">
@@ -3964,16 +4127,16 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>351847.93</v>
+        <v>428664.01</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>427073.59</v>
+        <v>420326.77</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>500708.01</v>
+        <v>409888.97</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>532211.03</v>
+        <v>539195.42</v>
       </c>
     </row>
     <row r="7">
@@ -3983,16 +4146,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>827793.33</v>
+        <v>1032804.72</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1035231.57</v>
+        <v>1010127.84</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1009904.95</v>
+        <v>886190.0600000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>600178.34</v>
+        <v>511573.72</v>
       </c>
     </row>
     <row r="8">
@@ -4002,16 +4165,16 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1465991.08</v>
+        <v>1569963.56</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>1568404.33</v>
+        <v>1561202.36</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1546579.6</v>
+        <v>1465652.73</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1533550.44</v>
+        <v>1543056.84</v>
       </c>
     </row>
     <row r="9">
@@ -4021,16 +4184,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>344948.95</v>
+        <v>420258.83</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>418699.6</v>
+        <v>412085.07</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>490890.21</v>
+        <v>401851.93</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>521775.52</v>
+        <v>528622.96</v>
       </c>
     </row>
     <row r="10">
@@ -4059,16 +4222,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>344948.95</v>
+        <v>420258.83</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>418699.6</v>
+        <v>412085.07</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>490890.21</v>
+        <v>401851.93</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>521775.52</v>
+        <v>528622.96</v>
       </c>
     </row>
     <row r="12">
@@ -4078,16 +4241,16 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>1121042.13</v>
+        <v>1149704.73</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>1149704.73</v>
+        <v>1149117.29</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>1055689.39</v>
+        <v>1063800.8</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>1011774.92</v>
+        <v>1014433.88</v>
       </c>
     </row>
     <row r="13">
@@ -4097,16 +4260,16 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1.046</v>
+        <v>1.264</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>1.265</v>
+        <v>1.238</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.422</v>
+        <v>1.211</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1.109</v>
+        <v>1.025</v>
       </c>
     </row>
     <row r="14">
@@ -4116,16 +4279,16 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>0.431</v>
+        <v>0.533</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>0.536</v>
+        <v>0.52</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.492</v>
+        <v>0.455</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.077</v>
+        <v>-0.017</v>
       </c>
     </row>
     <row r="15">
@@ -4135,16 +4298,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>234548.46</v>
+        <v>290612.71</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>290786.23</v>
+        <v>284442.58</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>300159.03</v>
+        <v>257608.4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>224390.77</v>
+        <v>208039.34</v>
       </c>
     </row>
     <row r="16">
@@ -4154,16 +4317,16 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>886493.67</v>
+        <v>859092.02</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>858918.5</v>
+        <v>864674.71</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>755530.36</v>
+        <v>806192.4</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>787384.15</v>
+        <v>806394.54</v>
       </c>
     </row>
     <row r="17">
@@ -4179,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
@@ -4226,16 +4389,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>827793.33</v>
+        <v>1032804.72</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1035231.57</v>
+        <v>1010127.84</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1009904.95</v>
+        <v>886190.0600000001</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>600178.34</v>
+        <v>511573.72</v>
       </c>
     </row>
     <row r="22">
@@ -4264,16 +4427,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>827793.33</v>
+        <v>1032804.72</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1035231.57</v>
+        <v>1010127.84</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1009904.95</v>
+        <v>886190.0600000001</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>600178.34</v>
+        <v>511573.72</v>
       </c>
     </row>
     <row r="24">
@@ -4302,16 +4465,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>827793.33</v>
+        <v>1032804.72</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1035231.57</v>
+        <v>1010127.84</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1009904.95</v>
+        <v>886190.0600000001</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>600178.34</v>
+        <v>511573.72</v>
       </c>
     </row>
     <row r="26">
@@ -4321,16 +4484,16 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>6898.98</v>
+        <v>8405.18</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>8373.99</v>
+        <v>8241.700000000001</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>9817.799999999999</v>
+        <v>8037.04</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>10435.51</v>
+        <v>10572.46</v>
       </c>
     </row>
     <row r="27">
@@ -4340,16 +4503,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>6898.98</v>
+        <v>8405.18</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>8373.99</v>
+        <v>8241.700000000001</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>9817.799999999999</v>
+        <v>8037.04</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>10435.51</v>
+        <v>10572.46</v>
       </c>
     </row>
     <row r="28">
@@ -4359,16 +4522,16 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>344948.95</v>
+        <v>420258.83</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>418699.6</v>
+        <v>412085.07</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>490890.21</v>
+        <v>401851.93</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>521775.52</v>
+        <v>528622.96</v>
       </c>
     </row>
     <row r="29">
@@ -4378,16 +4541,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>344948.95</v>
+        <v>420258.83</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>418699.6</v>
+        <v>412085.07</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>490890.21</v>
+        <v>401851.93</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>521775.52</v>
+        <v>528622.96</v>
       </c>
     </row>
     <row r="30">
@@ -4416,16 +4579,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>6898.98</v>
+        <v>8405.18</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8373.99</v>
+        <v>8241.700000000001</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9817.799999999999</v>
+        <v>8037.04</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10435.51</v>
+        <v>10572.46</v>
       </c>
     </row>
     <row r="32">
@@ -4435,16 +4598,16 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>286349.82</v>
+        <v>108494.83</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>106099.17</v>
+        <v>130747.75</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>35966.64</v>
+        <v>169573.7</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>401161.07</v>
+        <v>492287.7</v>
       </c>
     </row>
     <row r="33">
@@ -4454,16 +4617,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1121042.13</v>
+        <v>1149704.73</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1149704.73</v>
+        <v>1149117.29</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1055689.39</v>
+        <v>1063800.8</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1011774.92</v>
+        <v>1014433.88</v>
       </c>
     </row>
     <row r="34">
@@ -4526,16 +4689,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>566922.75</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>468937.27</v>
+        <v>498262.04</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>319230.74</v>
+        <v>412987.75</v>
       </c>
     </row>
     <row r="40">
@@ -4551,10 +4714,10 @@
         <v>0</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>99198.59</v>
+        <v>71653.28999999999</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>192958.99</v>
+        <v>195330.49</v>
       </c>
     </row>
     <row r="41">
@@ -4570,10 +4733,10 @@
         <v>0</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>96238.08</v>
+        <v>68847.19</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>261745.76</v>
+        <v>169589.98</v>
       </c>
     </row>
     <row r="42">
@@ -4583,16 +4746,16 @@
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="C42" s="12" t="n">
         <v>566922.75</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>664373.9399999999</v>
+        <v>638762.52</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>773935.49</v>
+        <v>777908.22</v>
       </c>
     </row>
     <row r="43">
@@ -4608,10 +4771,10 @@
         <v>0</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>97253.52</v>
+        <v>70248.32000000001</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>189175.48</v>
+        <v>191500.48</v>
       </c>
     </row>
     <row r="44">
@@ -4646,10 +4809,10 @@
         <v>0</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>97253.52</v>
+        <v>70248.32000000001</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>189175.48</v>
+        <v>191500.48</v>
       </c>
     </row>
     <row r="46">
@@ -4659,16 +4822,16 @@
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="C46" s="12" t="n">
         <v>566922.75</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>567120.42</v>
+        <v>568514.2</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>584760.01</v>
+        <v>586407.74</v>
       </c>
     </row>
     <row r="47">
@@ -4684,10 +4847,10 @@
         <v>0</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.341</v>
+        <v>0.245</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.771</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="48">
@@ -4706,7 +4869,7 @@
         <v>-0.002</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>0.124</v>
+        <v>-0.037</v>
       </c>
     </row>
     <row r="49">
@@ -4722,10 +4885,10 @@
         <v>0</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>38698.32</v>
+        <v>27819.1</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>90184.25</v>
+        <v>72218.09</v>
       </c>
     </row>
     <row r="50">
@@ -4735,16 +4898,16 @@
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="C50" s="12" t="n">
         <v>566922.75</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>528422.1</v>
+        <v>540695.1</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>494575.76</v>
+        <v>514189.65</v>
       </c>
     </row>
     <row r="51">
@@ -4760,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>0</v>
@@ -4813,10 +4976,10 @@
         <v>0</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>96238.08</v>
+        <v>68847.19</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>261745.76</v>
+        <v>169589.98</v>
       </c>
     </row>
     <row r="56">
@@ -4851,10 +5014,10 @@
         <v>0</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>96238.08</v>
+        <v>68847.19</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>261745.76</v>
+        <v>169589.98</v>
       </c>
     </row>
     <row r="58">
@@ -4889,10 +5052,10 @@
         <v>0</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>96238.08</v>
+        <v>68847.19</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>261745.76</v>
+        <v>169589.98</v>
       </c>
     </row>
     <row r="60">
@@ -4908,10 +5071,10 @@
         <v>0</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>1945.07</v>
+        <v>1404.97</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>3783.51</v>
+        <v>3830.01</v>
       </c>
     </row>
     <row r="61">
@@ -4927,10 +5090,10 @@
         <v>0</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1945.07</v>
+        <v>1404.97</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>3783.51</v>
+        <v>3830.01</v>
       </c>
     </row>
     <row r="62">
@@ -4946,10 +5109,10 @@
         <v>0</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>97253.52</v>
+        <v>70248.32000000001</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>189175.48</v>
+        <v>191500.48</v>
       </c>
     </row>
     <row r="63">
@@ -4965,10 +5128,10 @@
         <v>0</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>97253.52</v>
+        <v>70248.32000000001</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>189175.48</v>
+        <v>191500.48</v>
       </c>
     </row>
     <row r="64">
@@ -5003,10 +5166,10 @@
         <v>0</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>1945.07</v>
+        <v>1404.97</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>3783.51</v>
+        <v>3830.01</v>
       </c>
     </row>
     <row r="66">
@@ -5016,16 +5179,16 @@
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="C66" s="12" t="n">
         <v>566922.75</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>468937.27</v>
+        <v>498262.04</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>319230.74</v>
+        <v>412987.75</v>
       </c>
     </row>
     <row r="67">
@@ -5035,16 +5198,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="C67" s="4" t="n">
         <v>566922.75</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>567120.42</v>
+        <v>568514.2</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>584760.01</v>
+        <v>586407.74</v>
       </c>
     </row>
     <row r="68">
@@ -5116,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>81930.33</v>
+        <v>79299.95</v>
       </c>
     </row>
     <row r="74">
@@ -5126,16 +5289,16 @@
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>351847.93</v>
+        <v>428664.01</v>
       </c>
       <c r="C74" s="12" t="n">
-        <v>427073.59</v>
+        <v>420326.77</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>401509.42</v>
+        <v>338235.68</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>339252.04</v>
+        <v>343864.93</v>
       </c>
     </row>
     <row r="75">
@@ -5145,16 +5308,16 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>827793.33</v>
+        <v>1032804.72</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1035231.57</v>
+        <v>1010127.84</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>913666.87</v>
+        <v>817342.87</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>338432.58</v>
+        <v>341983.74</v>
       </c>
     </row>
     <row r="76">
@@ -5164,16 +5327,16 @@
         </is>
       </c>
       <c r="B76" s="12" t="n">
-        <v>1179641.26</v>
+        <v>1461468.73</v>
       </c>
       <c r="C76" s="12" t="n">
-        <v>1462305.16</v>
+        <v>1430454.61</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1315176.29</v>
+        <v>1155578.55</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>759614.95</v>
+        <v>765148.62</v>
       </c>
     </row>
     <row r="77">
@@ -5183,16 +5346,16 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
-        <v>344948.95</v>
+        <v>420258.83</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>418699.6</v>
+        <v>412085.07</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>393636.69</v>
+        <v>331603.61</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>332600.04</v>
+        <v>337122.48</v>
       </c>
     </row>
     <row r="78">
@@ -5202,13 +5365,13 @@
         </is>
       </c>
       <c r="B78" s="12" t="n">
-        <v>284519.99</v>
+        <v>458427.92</v>
       </c>
       <c r="C78" s="12" t="n">
-        <v>460823.58</v>
+        <v>436175</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>432970.63</v>
+        <v>328688.34</v>
       </c>
       <c r="E78" s="14" t="n">
         <v>0</v>
@@ -5221,16 +5384,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>629468.9399999999</v>
+        <v>878686.75</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>879523.1800000001</v>
+        <v>848260.0699999999</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>826607.3199999999</v>
+        <v>660291.95</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>332600.04</v>
+        <v>337122.48</v>
       </c>
     </row>
     <row r="80">
@@ -5240,16 +5403,16 @@
         </is>
       </c>
       <c r="B80" s="12" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="C80" s="12" t="n">
-        <v>582781.98</v>
+        <v>582194.54</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>488568.97</v>
+        <v>495286.6</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>427014.91</v>
+        <v>428026.14</v>
       </c>
     </row>
     <row r="81">
@@ -5259,16 +5422,16 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>2.132</v>
+        <v>2.493</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>2.495</v>
+        <v>2.443</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>2.676</v>
+        <v>2.32</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>1.571</v>
+        <v>1.587</v>
       </c>
     </row>
     <row r="82">
@@ -5278,16 +5441,16 @@
         </is>
       </c>
       <c r="B82" s="16" t="n">
-        <v>0.878</v>
+        <v>1.051</v>
       </c>
       <c r="C82" s="16" t="n">
-        <v>1.058</v>
+        <v>1.027</v>
       </c>
       <c r="D82" s="16" t="n">
-        <v>1.064</v>
+        <v>0.981</v>
       </c>
       <c r="E82" s="16" t="n">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="83">
@@ -5297,16 +5460,16 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>234548.46</v>
+        <v>290612.71</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>290786.23</v>
+        <v>284442.58</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>261460.71</v>
+        <v>229789.3</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>134206.52</v>
+        <v>135821.24</v>
       </c>
     </row>
     <row r="84">
@@ -5316,16 +5479,16 @@
         </is>
       </c>
       <c r="B84" s="12" t="n">
-        <v>315623.86</v>
+        <v>292169.27</v>
       </c>
       <c r="C84" s="12" t="n">
-        <v>291995.75</v>
+        <v>297751.96</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>227108.26</v>
+        <v>265497.3</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>292808.39</v>
+        <v>292204.9</v>
       </c>
     </row>
     <row r="85">
@@ -5344,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5388,16 +5551,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>582781.98</v>
+        <v>582194.54</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>488568.97</v>
+        <v>495286.6</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>338432.58</v>
+        <v>341983.74</v>
       </c>
     </row>
     <row r="90">
@@ -5426,16 +5589,16 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>827793.33</v>
+        <v>1032804.72</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1035231.57</v>
+        <v>1010127.84</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>913666.87</v>
+        <v>817342.87</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>338432.58</v>
+        <v>341983.74</v>
       </c>
     </row>
     <row r="92">
@@ -5445,13 +5608,13 @@
         </is>
       </c>
       <c r="B92" s="12" t="n">
-        <v>277621.01</v>
+        <v>450022.74</v>
       </c>
       <c r="C92" s="12" t="n">
-        <v>452449.59</v>
+        <v>427933.3</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>425097.9</v>
+        <v>322056.27</v>
       </c>
       <c r="E92" s="14" t="n">
         <v>0</v>
@@ -5464,16 +5627,16 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>582781.98</v>
+        <v>582194.54</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>488568.97</v>
+        <v>495286.6</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>338432.58</v>
+        <v>341983.74</v>
       </c>
     </row>
     <row r="94">
@@ -5492,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>6652</v>
+        <v>6742.45</v>
       </c>
     </row>
     <row r="95">
@@ -5511,7 +5674,7 @@
         <v>0</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>6652</v>
+        <v>6742.45</v>
       </c>
     </row>
     <row r="96">
@@ -5521,16 +5684,16 @@
         </is>
       </c>
       <c r="B96" s="12" t="n">
-        <v>344948.95</v>
+        <v>420258.83</v>
       </c>
       <c r="C96" s="12" t="n">
-        <v>418699.6</v>
+        <v>412085.07</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>393636.69</v>
+        <v>331603.61</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>332600.04</v>
+        <v>337122.48</v>
       </c>
     </row>
     <row r="97">
@@ -5540,16 +5703,16 @@
         </is>
       </c>
       <c r="B97" s="4" t="n">
-        <v>344948.95</v>
+        <v>420258.83</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>418699.6</v>
+        <v>412085.07</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>393636.69</v>
+        <v>331603.61</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>332600.04</v>
+        <v>337122.48</v>
       </c>
     </row>
     <row r="98">
@@ -5559,13 +5722,13 @@
         </is>
       </c>
       <c r="B98" s="12" t="n">
-        <v>6898.98</v>
+        <v>8405.18</v>
       </c>
       <c r="C98" s="12" t="n">
-        <v>8373.99</v>
+        <v>8241.700000000001</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>7872.73</v>
+        <v>6632.07</v>
       </c>
       <c r="E98" s="14" t="n">
         <v>0</v>
@@ -5587,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>6652</v>
+        <v>6742.45</v>
       </c>
     </row>
     <row r="100">
@@ -5606,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>81930.33</v>
+        <v>79299.95</v>
       </c>
     </row>
     <row r="101">
@@ -5616,16 +5779,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>582781.98</v>
+        <v>582194.54</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>488568.97</v>
+        <v>495286.6</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>427014.91</v>
+        <v>428026.14</v>
       </c>
     </row>
     <row r="102">
@@ -5718,17 +5881,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n">
-        <v>-28662.6</v>
+      <c r="B5" s="4" t="n">
+        <v>587.4400000000001</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>65352.74</v>
+        <v>85903.92999999999</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>109267.21</v>
+        <v>135270.85</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>199543.34</v>
+        <v>228205.94</v>
       </c>
     </row>
     <row r="6">
@@ -5757,7 +5920,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>39501.84</v>
+        <v>77359.05</v>
       </c>
     </row>
     <row r="9">
@@ -5800,17 +5963,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>3947.06</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>3749.39</v>
+      <c r="B11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>-1591.45</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>-13890.2</v>
+        <v>-19484.99</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>61537.87</v>
+        <v>57590.81</v>
       </c>
     </row>
     <row r="12">
@@ -5882,17 +6045,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
-        <v>-32609.66</v>
+      <c r="B17" s="4" t="n">
+        <v>587.4400000000001</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>61603.35</v>
+        <v>87495.38</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>123157.41</v>
+        <v>154755.84</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>138005.47</v>
+        <v>170615.13</v>
       </c>
     </row>
     <row r="18">
@@ -5902,16 +6065,16 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>38.98</v>
+        <v>62.8</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>194.88</v>
+        <v>313.99</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>818.48</v>
+        <v>1318.77</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>6080.15</v>
+        <v>9733.74</v>
       </c>
     </row>
     <row r="19">
@@ -5921,7 +6084,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>39501.84</v>
+        <v>77359.05</v>
       </c>
     </row>
     <row r="21">
@@ -6003,13 +6166,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1149704.73</v>
+        <v>1149117.29</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1055689.39</v>
+        <v>1063800.8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1011774.92</v>
+        <v>1014433.88</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -6021,17 +6184,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>-28662.6</v>
+      <c r="B6" s="12" t="n">
+        <v>587.4400000000001</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>65352.74</v>
+        <v>85903.92999999999</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>109267.21</v>
+        <v>135270.85</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>199543.34</v>
+        <v>228205.94</v>
       </c>
     </row>
     <row r="7">
@@ -6079,16 +6242,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1121042.13</v>
+        <v>1149704.73</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1121042.13</v>
+        <v>1149704.73</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1121042.13</v>
+        <v>1149704.73</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1121042.13</v>
+        <v>1149704.73</v>
       </c>
     </row>
     <row r="10">
@@ -6097,17 +6260,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="C10" s="21" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>21.65</v>
+      <c r="B10" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>24.76</v>
       </c>
     </row>
     <row r="11">
@@ -6116,16 +6279,16 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="C11" s="22" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="D11" s="22" t="n">
+      <c r="B11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="D11" s="21" t="n">
         <v>-9.41</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="21" t="n">
         <v>-9.470000000000001</v>
       </c>
     </row>
@@ -6173,10 +6336,10 @@
         <v>566922.75</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>567120.42</v>
+        <v>568514.2</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>584760.01</v>
+        <v>586407.74</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -6188,17 +6351,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>3947.06</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>3749.39</v>
-      </c>
-      <c r="D16" s="19" t="n">
-        <v>-13890.2</v>
+      <c r="B16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="22" t="n">
+        <v>-1591.45</v>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>-19484.99</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>61537.87</v>
+        <v>57590.81</v>
       </c>
     </row>
     <row r="17">
@@ -6246,16 +6409,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
     </row>
     <row r="20">
@@ -6264,17 +6427,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B20" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C20" s="21" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="D20" s="20" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="E20" s="21" t="n">
-        <v>12.08</v>
+      <c r="B20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>11.31</v>
       </c>
     </row>
     <row r="21">
@@ -6283,16 +6446,16 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="D21" s="22" t="n">
-        <v>-3.27</v>
-      </c>
-      <c r="E21" s="22" t="n">
+      <c r="B21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="E21" s="21" t="n">
         <v>-9.57</v>
       </c>
     </row>
@@ -6337,13 +6500,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>582781.98</v>
+        <v>582194.54</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>488568.97</v>
+        <v>495286.6</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>427014.91</v>
+        <v>428026.14</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -6355,17 +6518,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
-        <v>-32609.66</v>
+      <c r="B26" s="12" t="n">
+        <v>587.4400000000001</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>61603.35</v>
+        <v>87495.38</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>123157.41</v>
+        <v>154755.84</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>138005.47</v>
+        <v>170615.13</v>
       </c>
     </row>
     <row r="27">
@@ -6413,16 +6576,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
     </row>
     <row r="30">
@@ -6431,17 +6594,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="C30" s="21" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="D30" s="21" t="n">
-        <v>28.84</v>
-      </c>
-      <c r="E30" s="21" t="n">
-        <v>33.48</v>
+      <c r="B30" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>36.16</v>
+      </c>
+      <c r="E30" s="19" t="n">
+        <v>41.39</v>
       </c>
     </row>
     <row r="31">
@@ -6450,16 +6613,16 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="C31" s="22" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="D31" s="22" t="n">
+      <c r="B31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="21" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="D31" s="21" t="n">
         <v>-18.48</v>
       </c>
-      <c r="E31" s="22" t="n">
+      <c r="E31" s="21" t="n">
         <v>-18.48</v>
       </c>
     </row>
@@ -6510,7 +6673,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>65352.74</v>
+        <v>85903.92999999999</v>
       </c>
     </row>
     <row r="5">
@@ -6519,8 +6682,8 @@
           <t>Investing cash flow</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>36170.36</v>
+      <c r="B5" s="18" t="n">
+        <v>-128207.76</v>
       </c>
     </row>
     <row r="6">
@@ -6539,8 +6702,8 @@
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>101523.1</v>
+      <c r="B7" s="18" t="n">
+        <v>-42303.83</v>
       </c>
     </row>
     <row r="8">
@@ -6550,7 +6713,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>35966.64</v>
+        <v>169573.7</v>
       </c>
     </row>
     <row r="9">
@@ -6560,7 +6723,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>286349.82</v>
+        <v>108494.83</v>
       </c>
     </row>
     <row r="11">
@@ -6584,7 +6747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8158,16 +8321,6 @@
       </c>
       <c r="B158" s="4" t="n">
         <v>1149704.73</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="B159" s="12" t="n">
-        <v>1121042.13</v>
       </c>
     </row>
   </sheetData>
@@ -8272,34 +8425,34 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1121042.13</v>
+        <v>1149704.73</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>827793.33</v>
+        <v>1032804.72</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>344948.95</v>
+        <v>420258.83</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1172742.28</v>
+        <v>1453063.55</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>482844.38</v>
+        <v>612545.89</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.046</v>
+        <v>1.264</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.431</v>
+        <v>0.533</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>104.61</v>
+        <v>126.39</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>52.31</v>
+        <v>63.19</v>
       </c>
       <c r="K4" s="24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -8309,7 +8462,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>0</v>
@@ -8346,34 +8499,34 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>827793.33</v>
+        <v>1032804.72</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>344948.95</v>
+        <v>420258.83</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1172742.28</v>
+        <v>1453063.55</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>482844.38</v>
+        <v>612545.89</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.132</v>
+        <v>2.493</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.878</v>
+        <v>1.051</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>213.16</v>
+        <v>249.33</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>106.58</v>
+        <v>124.67</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -8390,7 +8543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8411,7 +8564,7 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>HHI=0.1493  ·  effective N pairs=6.7  ·  max pair=21.32% of gross</t>
+          <t>HHI=0.132  ·  effective N pairs=7.6  ·  max pair=17.52% of gross</t>
         </is>
       </c>
     </row>
@@ -8454,16 +8607,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>270556.2</v>
+        <v>292318.8</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>270556.2</v>
-      </c>
-      <c r="D6" s="23" t="n">
-        <v>24.13</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>23.07</v>
+        <v>292318.8</v>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>20.12</v>
       </c>
       <c r="F6" s="24" t="n">
         <v>2</v>
@@ -8472,67 +8625,67 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>175583.07</v>
+        <v>276000.66</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>175583.07</v>
-      </c>
-      <c r="D7" s="21" t="n">
-        <v>15.66</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>14.97</v>
+        <v>276000.66</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>18.99</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>123801.64</v>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>-123801.64</v>
-      </c>
-      <c r="D8" s="23" t="n">
-        <v>11.04</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>10.56</v>
+        <v>181006.02</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>181006.02</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>12.46</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>105875.94</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>105875.94</v>
-      </c>
-      <c r="D9" s="21" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>9.029999999999999</v>
+        <v>122411.98</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <v>-122411.98</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>8.42</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -8542,16 +8695,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>99282.52</v>
+        <v>104619.48</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>99282.52</v>
-      </c>
-      <c r="D10" s="23" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>8.470000000000001</v>
+        <v>104619.48</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>7.2</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>1</v>
@@ -8564,16 +8717,16 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>91258.28</v>
+        <v>93543.48</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>91258.28</v>
-      </c>
-      <c r="D11" s="21" t="n">
+        <v>93543.48</v>
+      </c>
+      <c r="D11" s="19" t="n">
         <v>8.140000000000001</v>
       </c>
-      <c r="E11" s="21" t="n">
-        <v>7.78</v>
+      <c r="E11" s="19" t="n">
+        <v>6.44</v>
       </c>
       <c r="F11" s="26" t="n">
         <v>1</v>
@@ -8586,16 +8739,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>85237.32000000001</v>
+        <v>85316.28</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>85237.32000000001</v>
-      </c>
-      <c r="D12" s="23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>7.27</v>
+        <v>85316.28</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>5.87</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>1</v>
@@ -8604,20 +8757,20 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>52669.82</v>
-      </c>
-      <c r="C13" s="19" t="n">
-        <v>-52669.82</v>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>4.49</v>
+        <v>78762.92999999999</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>-78762.92999999999</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>5.42</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>1</v>
@@ -8630,16 +8783,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>52590.2</v>
+        <v>52257.26</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>-52590.2</v>
-      </c>
-      <c r="D14" s="23" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="E14" s="23" t="n">
-        <v>4.48</v>
+        <v>-52257.26</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>3.6</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>1</v>
@@ -8652,16 +8805,16 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>52179.5</v>
-      </c>
-      <c r="C15" s="19" t="n">
-        <v>-52179.5</v>
-      </c>
-      <c r="D15" s="21" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>4.45</v>
+        <v>51508</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>-51508</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>3.54</v>
       </c>
       <c r="F15" s="26" t="n">
         <v>1</v>
@@ -8708,16 +8861,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>545421.79</v>
+        <v>577944.3</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>102238.82</v>
+        <v>101174.12</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>443182.97</v>
+        <v>476770.18</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>37.79</v>
+        <v>32.81</v>
       </c>
     </row>
     <row r="21">
@@ -8727,73 +8880,92 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>191113.26</v>
+        <v>361316.94</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>191113.26</v>
+        <v>361316.94</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>16.3</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>food</t>
         </is>
       </c>
       <c r="B22" s="17" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>66728.99000000001</v>
+        <v>78762.92999999999</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>-66728.99000000001</v>
+        <v>-78762.92999999999</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-5.69</v>
+        <v>-5.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>utilities</t>
+          <t>health</t>
         </is>
       </c>
       <c r="B23" s="14" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>52179.5</v>
-      </c>
-      <c r="D23" s="19" t="n">
-        <v>-52179.5</v>
+        <v>66401.8</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>-66401.8</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>-4.45</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
+          <t>utilities</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>51508</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>-51508</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>-3.54</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>91258.28</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>123801.64</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>-32543.36</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>-2.77</v>
+      <c r="B25" s="12" t="n">
+        <v>93543.48</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>122411.98</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>-28868.5</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>-1.99</v>
       </c>
     </row>
   </sheetData>
@@ -8810,7 +8982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8831,7 +9003,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1.321</v>
+        <v>1.355</v>
       </c>
     </row>
     <row r="4">
@@ -8841,7 +9013,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1.877</v>
+        <v>2.056</v>
       </c>
     </row>
     <row r="5">
@@ -8851,7 +9023,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>43.07</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="6">
@@ -8891,8 +9063,8 @@
           <t>tech</t>
         </is>
       </c>
-      <c r="B10" s="23" t="n">
-        <v>37.79</v>
+      <c r="B10" s="20" t="n">
+        <v>32.81</v>
       </c>
     </row>
     <row r="11">
@@ -8901,38 +9073,48 @@
           <t>materials</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n">
-        <v>16.3</v>
+      <c r="B11" s="19" t="n">
+        <v>24.87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>health</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="n">
-        <v>-5.69</v>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="n">
+        <v>-5.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>utilities</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="n">
-        <v>-4.45</v>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>-4.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
+          <t>utilities</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="n">
+        <v>-3.54</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
-        <v>-2.77</v>
+      <c r="B15" s="23" t="n">
+        <v>-1.99</v>
       </c>
     </row>
   </sheetData>
